--- a/latest-events.xlsx
+++ b/latest-events.xlsx
@@ -422,7 +422,7 @@
         <v>6618</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-08-24 09:52:37</v>
+        <v>2026-09-14 08:49:21</v>
       </c>
       <c r="D2" t="str">
         <v>NO</v>
@@ -430,13 +430,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>GC MAXUS PCRF-25 TERRENO</v>
+        <v>GC MAXUS PKFF-65 G VICENCIO</v>
       </c>
       <c r="B3">
-        <v>6617</v>
+        <v>6616</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-08-24 12:18:21</v>
+        <v>2026-09-14 09:46:25</v>
       </c>
       <c r="D3" t="str">
         <v>NO</v>
@@ -444,13 +444,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>GC MAXUS PKFF-65 G VICENCIO</v>
+        <v>GC RXDL-59 OPERACIONES</v>
       </c>
       <c r="B4">
-        <v>6616</v>
+        <v>6581</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-08-24 09:46:56</v>
+        <v>2026-09-15 17:15:57</v>
       </c>
       <c r="D4" t="str">
         <v>NO</v>
@@ -464,7 +464,7 @@
         <v>6608</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-08-24 10:22:58</v>
+        <v>2026-09-14 09:00:31</v>
       </c>
       <c r="D5" t="str">
         <v>NO</v>
@@ -478,7 +478,7 @@
         <v>6609</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-08-24 11:18:17</v>
+        <v>2026-09-14 10:32:16</v>
       </c>
       <c r="D6" t="str">
         <v>NO</v>
@@ -492,7 +492,7 @@
         <v>6620</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-08-24 11:23:41</v>
+        <v>2026-09-14 12:01:24</v>
       </c>
       <c r="D7" t="str">
         <v>NO</v>
@@ -506,7 +506,7 @@
         <v>6610</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-08-24 18:02:29</v>
+        <v>2026-09-14 08:52:24</v>
       </c>
       <c r="D8" t="str">
         <v>NO</v>
@@ -520,7 +520,7 @@
         <v>6583</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-08-24 15:49:00</v>
+        <v>2026-09-17 12:36:14</v>
       </c>
       <c r="D9" t="str">
         <v>NO</v>
@@ -534,7 +534,7 @@
         <v>6593</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-08-24 12:38:38</v>
+        <v>2026-09-14 11:31:48</v>
       </c>
       <c r="D10" t="str">
         <v>NO</v>
@@ -548,10 +548,10 @@
         <v>6597</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-08-24 06:52:18</v>
+        <v>2026-09-14 07:29:04</v>
       </c>
       <c r="D11" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="12">
@@ -562,7 +562,7 @@
         <v>6598</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-08-24 11:49:46</v>
+        <v>2026-09-14 09:59:55</v>
       </c>
       <c r="D12" t="str">
         <v>NO</v>
@@ -576,7 +576,7 @@
         <v>6586</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-08-24 12:02:22</v>
+        <v>2026-09-14 11:06:46</v>
       </c>
       <c r="D13" t="str">
         <v>NO</v>
@@ -590,7 +590,7 @@
         <v>6604</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-08-24 12:53:48</v>
+        <v>2026-09-15 12:03:20</v>
       </c>
       <c r="D14" t="str">
         <v>NO</v>
@@ -604,7 +604,7 @@
         <v>6601</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-08-24 13:31:21</v>
+        <v>2026-09-14 12:54:50</v>
       </c>
       <c r="D15" t="str">
         <v>NO</v>
@@ -618,7 +618,7 @@
         <v>6606</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-08-24 10:17:07</v>
+        <v>2026-09-14 09:27:56</v>
       </c>
       <c r="D16" t="str">
         <v>NO</v>
@@ -632,7 +632,7 @@
         <v>6580</v>
       </c>
       <c r="C17" t="str">
-        <v>2026-08-24 12:00:50</v>
+        <v>2026-09-14 10:59:29</v>
       </c>
       <c r="D17" t="str">
         <v>NO</v>
@@ -646,7 +646,7 @@
         <v>6594</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-08-24 11:58:25</v>
+        <v>2026-09-14 12:38:23</v>
       </c>
       <c r="D18" t="str">
         <v>NO</v>
@@ -660,7 +660,7 @@
         <v>6605</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-08-24 12:37:53</v>
+        <v>2026-09-14 12:10:23</v>
       </c>
       <c r="D19" t="str">
         <v>NO</v>
@@ -674,10 +674,10 @@
         <v>6603</v>
       </c>
       <c r="C20" t="str">
-        <v>2026-08-24 06:02:10</v>
+        <v>2026-09-14 10:01:40</v>
       </c>
       <c r="D20" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="21">
@@ -688,7 +688,7 @@
         <v>6607</v>
       </c>
       <c r="C21" t="str">
-        <v>2026-08-24 10:14:42</v>
+        <v>2026-09-14 09:29:50</v>
       </c>
       <c r="D21" t="str">
         <v>NO</v>
@@ -702,7 +702,7 @@
         <v>6602</v>
       </c>
       <c r="C22" t="str">
-        <v>2026-08-24 10:52:38</v>
+        <v>2026-09-14 13:26:51</v>
       </c>
       <c r="D22" t="str">
         <v>NO</v>
@@ -716,7 +716,7 @@
         <v>6612</v>
       </c>
       <c r="C23" t="str">
-        <v>2026-08-24 10:48:32</v>
+        <v>2026-09-14 10:52:37</v>
       </c>
       <c r="D23" t="str">
         <v>NO</v>
@@ -730,7 +730,7 @@
         <v>6599</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-08-24 11:52:41</v>
+        <v>2026-09-14 10:48:23</v>
       </c>
       <c r="D24" t="str">
         <v>NO</v>
@@ -744,10 +744,10 @@
         <v>6621</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-08-25 12:12:37</v>
+        <v>2026-09-14 19:17:50</v>
       </c>
       <c r="D25" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="26">
@@ -758,7 +758,7 @@
         <v>6592</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-08-24 08:16:27</v>
+        <v>2026-09-14 07:32:34</v>
       </c>
       <c r="D26" t="str">
         <v>NO</v>
@@ -772,7 +772,7 @@
         <v>6595</v>
       </c>
       <c r="C27" t="str">
-        <v>2026-08-24 11:13:59</v>
+        <v>2026-09-14 10:03:37</v>
       </c>
       <c r="D27" t="str">
         <v>NO</v>
@@ -786,7 +786,7 @@
         <v>6585</v>
       </c>
       <c r="C28" t="str">
-        <v>2026-08-24 11:16:07</v>
+        <v>2026-09-14 10:19:10</v>
       </c>
       <c r="D28" t="str">
         <v>NO</v>
@@ -800,7 +800,7 @@
         <v>6588</v>
       </c>
       <c r="C29" t="str">
-        <v>2026-08-24 12:12:41</v>
+        <v>2026-09-14 11:13:34</v>
       </c>
       <c r="D29" t="str">
         <v>NO</v>
@@ -814,7 +814,7 @@
         <v>6587</v>
       </c>
       <c r="C30" t="str">
-        <v>2026-08-24 11:24:36</v>
+        <v>2026-09-14 10:26:17</v>
       </c>
       <c r="D30" t="str">
         <v>NO</v>
@@ -828,7 +828,7 @@
         <v>6582</v>
       </c>
       <c r="C31" t="str">
-        <v>2026-08-24 11:54:32</v>
+        <v>2026-09-14 11:11:15</v>
       </c>
       <c r="D31" t="str">
         <v>NO</v>
@@ -842,10 +842,10 @@
         <v>6589</v>
       </c>
       <c r="C32" t="str">
-        <v>2026-08-24 12:01:27</v>
+        <v>2026-09-14 20:18:47</v>
       </c>
       <c r="D32" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="33">
@@ -856,7 +856,7 @@
         <v>6596</v>
       </c>
       <c r="C33" t="str">
-        <v>2026-08-24 12:08:13</v>
+        <v>2026-09-14 11:01:38</v>
       </c>
       <c r="D33" t="str">
         <v>NO</v>
@@ -870,10 +870,10 @@
         <v>6619</v>
       </c>
       <c r="C34" t="str">
-        <v>2026-08-24 11:30:02</v>
+        <v>2026-09-14 19:09:39</v>
       </c>
       <c r="D34" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="35">
@@ -884,10 +884,10 @@
         <v>6614</v>
       </c>
       <c r="C35" t="str">
-        <v>2026-08-26 19:53:11</v>
+        <v>2026-09-14 08:50:46</v>
       </c>
       <c r="D35" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
   </sheetData>
@@ -917,10 +917,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
+        <v>GV FORD BU-9781 V OLIVARES</v>
       </c>
       <c r="B2">
-        <v>6597</v>
+        <v>6621</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -931,10 +931,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>GP CHANGAN RRDF-75 L LOBOS</v>
+        <v>GV TM5 RXXG-15 E CABANILLA</v>
       </c>
       <c r="B3">
-        <v>6603</v>
+        <v>6589</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>JAC  LYTS-17 G GALEA</v>
+        <v>GV TOLVA SPGW-29 V OLIVARES</v>
       </c>
       <c r="B4">
-        <v>6614</v>
+        <v>6619</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>GC MAXUS PCRF-25 TERRENO</v>
+        <v>GC MAXUS PKFF-65 G VICENCIO</v>
       </c>
       <c r="B6">
-        <v>6617</v>
+        <v>6616</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -987,10 +987,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>GC MAXUS PKFF-65 G VICENCIO</v>
+        <v>GC RXDL-59 OPERACIONES</v>
       </c>
       <c r="B7">
-        <v>6616</v>
+        <v>6581</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>GLP SHDV-51 J REBOLLEDO</v>
+        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
       </c>
       <c r="B14">
-        <v>6598</v>
+        <v>6597</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>GLP SHLC-75 L FONSECA</v>
+        <v>GLP SHDV-51 J REBOLLEDO</v>
       </c>
       <c r="B15">
-        <v>6586</v>
+        <v>6598</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>GLP SHXP-98 CAMION PLUMA</v>
+        <v>GLP SHLC-75 L FONSECA</v>
       </c>
       <c r="B16">
-        <v>6604</v>
+        <v>6586</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>GLP SHXP-99 ALZA HOMBRE</v>
+        <v>GLP SHXP-98 CAMION PLUMA</v>
       </c>
       <c r="B17">
-        <v>6601</v>
+        <v>6604</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1141,10 +1141,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>GLP SKDX-44 V VIAL</v>
+        <v>GLP SHXP-99 ALZA HOMBRE</v>
       </c>
       <c r="B18">
-        <v>6606</v>
+        <v>6601</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1155,10 +1155,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>GLP SSZD-71  J VALLEJOS</v>
+        <v>GLP SKDX-44 V VIAL</v>
       </c>
       <c r="B19">
-        <v>6580</v>
+        <v>6606</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
+        <v>GLP SSZD-71  J VALLEJOS</v>
       </c>
       <c r="B20">
-        <v>6594</v>
+        <v>6580</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>GP -SHLC-76 F SEPULVEDA</v>
+        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
       </c>
       <c r="B21">
-        <v>6605</v>
+        <v>6594</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1197,10 +1197,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>GP DONGFENG DF6-RXDL-60</v>
+        <v>GP -SHLC-76 F SEPULVEDA</v>
       </c>
       <c r="B22">
-        <v>6607</v>
+        <v>6605</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>GP FOTON G7 TSVS-96</v>
+        <v>GP CHANGAN RRDF-75 L LOBOS</v>
       </c>
       <c r="B23">
-        <v>6602</v>
+        <v>6603</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>GP TM5 TRRD-32 V PIZARRO</v>
+        <v>GP DONGFENG DF6-RXDL-60</v>
       </c>
       <c r="B24">
-        <v>6612</v>
+        <v>6607</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>GP TM5 TSDK-95 L MUNOZ</v>
+        <v>GP FOTON G7 TSVS-96</v>
       </c>
       <c r="B25">
-        <v>6599</v>
+        <v>6602</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>GV FORD BU-9781 V OLIVARES</v>
+        <v>GP TM5 TRRD-32 V PIZARRO</v>
       </c>
       <c r="B26">
-        <v>6621</v>
+        <v>6612</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>GV FOSERO SJHW-18 V OLIVARES</v>
+        <v>GP TM5 TSDK-95 L MUNOZ</v>
       </c>
       <c r="B27">
-        <v>6592</v>
+        <v>6599</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>GV PEUGEOT THJY-73 J PONCE</v>
+        <v>GV FOSERO SJHW-18 V OLIVARES</v>
       </c>
       <c r="B28">
-        <v>6595</v>
+        <v>6592</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1295,10 +1295,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>GV SHDV-50 C CARDENAS</v>
+        <v>GV PEUGEOT THJY-73 J PONCE</v>
       </c>
       <c r="B29">
-        <v>6585</v>
+        <v>6595</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1309,10 +1309,10 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>GV SHLC-74 B MIRANDA</v>
+        <v>GV SHDV-50 C CARDENAS</v>
       </c>
       <c r="B30">
-        <v>6588</v>
+        <v>6585</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1323,10 +1323,10 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>GV TDKV-88 L CORDERO</v>
+        <v>GV SHLC-74 B MIRANDA</v>
       </c>
       <c r="B31">
-        <v>6587</v>
+        <v>6588</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>GV TDLD-98 J PACHECHO</v>
+        <v>GV TDKV-88 L CORDERO</v>
       </c>
       <c r="B32">
-        <v>6582</v>
+        <v>6587</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>GV TM5 RXXG-15 E CABANILLA</v>
+        <v>GV TDLD-98 J PACHECHO</v>
       </c>
       <c r="B33">
-        <v>6589</v>
+        <v>6582</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>GV TOLVA SPGW-29 V OLIVARES</v>
+        <v>JAC  LYTS-17 G GALEA</v>
       </c>
       <c r="B35">
-        <v>6619</v>
+        <v>6614</v>
       </c>
       <c r="C35">
         <v>1</v>

--- a/latest-events.xlsx
+++ b/latest-events.xlsx
@@ -422,7 +422,7 @@
         <v>6618</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-09-14 08:49:21</v>
+        <v>2026-09-21 08:46:44</v>
       </c>
       <c r="D2" t="str">
         <v>NO</v>
@@ -430,13 +430,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>GC MAXUS PKFF-65 G VICENCIO</v>
+        <v>GC MAXUS PCRF-25 TERRENO</v>
       </c>
       <c r="B3">
-        <v>6616</v>
+        <v>6617</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-09-14 09:46:25</v>
+        <v>2026-09-22 13:42:24</v>
       </c>
       <c r="D3" t="str">
         <v>NO</v>
@@ -444,13 +444,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>GC RXDL-59 OPERACIONES</v>
+        <v>GC MAXUS PKFF-65 G VICENCIO</v>
       </c>
       <c r="B4">
-        <v>6581</v>
+        <v>6616</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-09-15 17:15:57</v>
+        <v>2026-09-21 10:02:14</v>
       </c>
       <c r="D4" t="str">
         <v>NO</v>
@@ -464,7 +464,7 @@
         <v>6608</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-09-14 09:00:31</v>
+        <v>2026-09-21 08:45:35</v>
       </c>
       <c r="D5" t="str">
         <v>NO</v>
@@ -478,7 +478,7 @@
         <v>6609</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-09-14 10:32:16</v>
+        <v>2026-09-21 10:18:47</v>
       </c>
       <c r="D6" t="str">
         <v>NO</v>
@@ -492,7 +492,7 @@
         <v>6620</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-09-14 12:01:24</v>
+        <v>2026-09-21 11:21:23</v>
       </c>
       <c r="D7" t="str">
         <v>NO</v>
@@ -506,7 +506,7 @@
         <v>6610</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-09-14 08:52:24</v>
+        <v>2026-09-21 10:34:55</v>
       </c>
       <c r="D8" t="str">
         <v>NO</v>
@@ -520,7 +520,7 @@
         <v>6583</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-09-17 12:36:14</v>
+        <v>2026-09-21 14:26:41</v>
       </c>
       <c r="D9" t="str">
         <v>NO</v>
@@ -534,7 +534,7 @@
         <v>6593</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-09-14 11:31:48</v>
+        <v>2026-09-21 11:35:08</v>
       </c>
       <c r="D10" t="str">
         <v>NO</v>
@@ -548,10 +548,10 @@
         <v>6597</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-09-14 07:29:04</v>
+        <v>2026-09-21 06:00:45</v>
       </c>
       <c r="D11" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="12">
@@ -562,7 +562,7 @@
         <v>6598</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-09-14 09:59:55</v>
+        <v>2026-09-21 10:00:02</v>
       </c>
       <c r="D12" t="str">
         <v>NO</v>
@@ -576,7 +576,7 @@
         <v>6586</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-09-14 11:06:46</v>
+        <v>2026-09-21 11:00:02</v>
       </c>
       <c r="D13" t="str">
         <v>NO</v>
@@ -590,7 +590,7 @@
         <v>6604</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-09-15 12:03:20</v>
+        <v>2026-09-21 18:44:12</v>
       </c>
       <c r="D14" t="str">
         <v>NO</v>
@@ -604,7 +604,7 @@
         <v>6601</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-09-14 12:54:50</v>
+        <v>2026-09-21 12:41:35</v>
       </c>
       <c r="D15" t="str">
         <v>NO</v>
@@ -618,7 +618,7 @@
         <v>6606</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-09-14 09:27:56</v>
+        <v>2026-09-21 11:50:45</v>
       </c>
       <c r="D16" t="str">
         <v>NO</v>
@@ -632,7 +632,7 @@
         <v>6580</v>
       </c>
       <c r="C17" t="str">
-        <v>2026-09-14 10:59:29</v>
+        <v>2026-09-21 10:58:18</v>
       </c>
       <c r="D17" t="str">
         <v>NO</v>
@@ -646,7 +646,7 @@
         <v>6594</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-09-14 12:38:23</v>
+        <v>2026-09-21 12:25:25</v>
       </c>
       <c r="D18" t="str">
         <v>NO</v>
@@ -660,7 +660,7 @@
         <v>6605</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-09-14 12:10:23</v>
+        <v>2026-09-21 12:37:55</v>
       </c>
       <c r="D19" t="str">
         <v>NO</v>
@@ -674,7 +674,7 @@
         <v>6603</v>
       </c>
       <c r="C20" t="str">
-        <v>2026-09-14 10:01:40</v>
+        <v>2026-09-21 12:47:19</v>
       </c>
       <c r="D20" t="str">
         <v>NO</v>
@@ -688,7 +688,7 @@
         <v>6607</v>
       </c>
       <c r="C21" t="str">
-        <v>2026-09-14 09:29:50</v>
+        <v>2026-09-21 09:47:05</v>
       </c>
       <c r="D21" t="str">
         <v>NO</v>
@@ -702,7 +702,7 @@
         <v>6602</v>
       </c>
       <c r="C22" t="str">
-        <v>2026-09-14 13:26:51</v>
+        <v>2026-09-21 11:50:34</v>
       </c>
       <c r="D22" t="str">
         <v>NO</v>
@@ -716,7 +716,7 @@
         <v>6612</v>
       </c>
       <c r="C23" t="str">
-        <v>2026-09-14 10:52:37</v>
+        <v>2026-09-21 10:19:47</v>
       </c>
       <c r="D23" t="str">
         <v>NO</v>
@@ -730,7 +730,7 @@
         <v>6599</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-09-14 10:48:23</v>
+        <v>2026-09-21 11:30:04</v>
       </c>
       <c r="D24" t="str">
         <v>NO</v>
@@ -744,7 +744,7 @@
         <v>6621</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-09-14 19:17:50</v>
+        <v>2026-09-22 20:57:49</v>
       </c>
       <c r="D25" t="str">
         <v>SI</v>
@@ -758,7 +758,7 @@
         <v>6592</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-09-14 07:32:34</v>
+        <v>2026-09-21 07:33:19</v>
       </c>
       <c r="D26" t="str">
         <v>NO</v>
@@ -772,7 +772,7 @@
         <v>6595</v>
       </c>
       <c r="C27" t="str">
-        <v>2026-09-14 10:03:37</v>
+        <v>2026-09-21 09:57:24</v>
       </c>
       <c r="D27" t="str">
         <v>NO</v>
@@ -786,7 +786,7 @@
         <v>6585</v>
       </c>
       <c r="C28" t="str">
-        <v>2026-09-14 10:19:10</v>
+        <v>2026-09-21 10:36:40</v>
       </c>
       <c r="D28" t="str">
         <v>NO</v>
@@ -800,10 +800,10 @@
         <v>6588</v>
       </c>
       <c r="C29" t="str">
-        <v>2026-09-14 11:13:34</v>
+        <v>2026-09-21 20:51:22</v>
       </c>
       <c r="D29" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="30">
@@ -814,7 +814,7 @@
         <v>6587</v>
       </c>
       <c r="C30" t="str">
-        <v>2026-09-14 10:26:17</v>
+        <v>2026-09-21 10:25:11</v>
       </c>
       <c r="D30" t="str">
         <v>NO</v>
@@ -828,7 +828,7 @@
         <v>6582</v>
       </c>
       <c r="C31" t="str">
-        <v>2026-09-14 11:11:15</v>
+        <v>2026-09-21 11:04:25</v>
       </c>
       <c r="D31" t="str">
         <v>NO</v>
@@ -842,7 +842,7 @@
         <v>6589</v>
       </c>
       <c r="C32" t="str">
-        <v>2026-09-14 20:18:47</v>
+        <v>2026-09-21 20:10:54</v>
       </c>
       <c r="D32" t="str">
         <v>SI</v>
@@ -856,7 +856,7 @@
         <v>6596</v>
       </c>
       <c r="C33" t="str">
-        <v>2026-09-14 11:01:38</v>
+        <v>2026-09-21 11:03:31</v>
       </c>
       <c r="D33" t="str">
         <v>NO</v>
@@ -870,7 +870,7 @@
         <v>6619</v>
       </c>
       <c r="C34" t="str">
-        <v>2026-09-14 19:09:39</v>
+        <v>2026-09-21 20:30:53</v>
       </c>
       <c r="D34" t="str">
         <v>SI</v>
@@ -884,7 +884,7 @@
         <v>6614</v>
       </c>
       <c r="C35" t="str">
-        <v>2026-09-14 08:50:46</v>
+        <v>2026-09-21 08:47:52</v>
       </c>
       <c r="D35" t="str">
         <v>NO</v>
@@ -917,10 +917,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>GV FORD BU-9781 V OLIVARES</v>
+        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
       </c>
       <c r="B2">
-        <v>6621</v>
+        <v>6597</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -931,10 +931,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>GV TM5 RXXG-15 E CABANILLA</v>
+        <v>GV FORD BU-9781 V OLIVARES</v>
       </c>
       <c r="B3">
-        <v>6589</v>
+        <v>6621</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>GV TOLVA SPGW-29 V OLIVARES</v>
+        <v>GV SHLC-74 B MIRANDA</v>
       </c>
       <c r="B4">
-        <v>6619</v>
+        <v>6588</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -959,38 +959,38 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>DONGFENG DF6 SRSR-97</v>
+        <v>GV TM5 RXXG-15 E CABANILLA</v>
       </c>
       <c r="B5">
-        <v>6618</v>
+        <v>6589</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>GC MAXUS PKFF-65 G VICENCIO</v>
+        <v>GV TOLVA SPGW-29 V OLIVARES</v>
       </c>
       <c r="B6">
-        <v>6616</v>
+        <v>6619</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>GC RXDL-59 OPERACIONES</v>
+        <v>DONGFENG DF6 SRSR-97</v>
       </c>
       <c r="B7">
-        <v>6581</v>
+        <v>6618</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>GC TM5-RXXG-13 D SILVA</v>
+        <v>GC MAXUS PCRF-25 TERRENO</v>
       </c>
       <c r="B8">
-        <v>6608</v>
+        <v>6617</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>GC TM5-VKFB-85 M CASTRO</v>
+        <v>GC MAXUS PKFF-65 G VICENCIO</v>
       </c>
       <c r="B9">
-        <v>6609</v>
+        <v>6616</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>GC TM5-VRVJ-20 L SALINAS</v>
+        <v>GC TM5-RXXG-13 D SILVA</v>
       </c>
       <c r="B10">
-        <v>6620</v>
+        <v>6608</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1043,10 +1043,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>GC TSVS-89 M AEDO</v>
+        <v>GC TM5-VKFB-85 M CASTRO</v>
       </c>
       <c r="B11">
-        <v>6610</v>
+        <v>6609</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1057,10 +1057,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>GLP ALJIBE SJHW-20</v>
+        <v>GC TM5-VRVJ-20 L SALINAS</v>
       </c>
       <c r="B12">
-        <v>6583</v>
+        <v>6620</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
+        <v>GC TSVS-89 M AEDO</v>
       </c>
       <c r="B13">
-        <v>6593</v>
+        <v>6610</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
+        <v>GLP ALJIBE SJHW-20</v>
       </c>
       <c r="B14">
-        <v>6597</v>
+        <v>6583</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>GLP SHDV-51 J REBOLLEDO</v>
+        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
       </c>
       <c r="B15">
-        <v>6598</v>
+        <v>6593</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>GLP SHLC-75 L FONSECA</v>
+        <v>GLP SHDV-51 J REBOLLEDO</v>
       </c>
       <c r="B16">
-        <v>6586</v>
+        <v>6598</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>GLP SHXP-98 CAMION PLUMA</v>
+        <v>GLP SHLC-75 L FONSECA</v>
       </c>
       <c r="B17">
-        <v>6604</v>
+        <v>6586</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1141,10 +1141,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>GLP SHXP-99 ALZA HOMBRE</v>
+        <v>GLP SHXP-98 CAMION PLUMA</v>
       </c>
       <c r="B18">
-        <v>6601</v>
+        <v>6604</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1155,10 +1155,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>GLP SKDX-44 V VIAL</v>
+        <v>GLP SHXP-99 ALZA HOMBRE</v>
       </c>
       <c r="B19">
-        <v>6606</v>
+        <v>6601</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>GLP SSZD-71  J VALLEJOS</v>
+        <v>GLP SKDX-44 V VIAL</v>
       </c>
       <c r="B20">
-        <v>6580</v>
+        <v>6606</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
+        <v>GLP SSZD-71  J VALLEJOS</v>
       </c>
       <c r="B21">
-        <v>6594</v>
+        <v>6580</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1197,10 +1197,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>GP -SHLC-76 F SEPULVEDA</v>
+        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
       </c>
       <c r="B22">
-        <v>6605</v>
+        <v>6594</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>GP CHANGAN RRDF-75 L LOBOS</v>
+        <v>GP -SHLC-76 F SEPULVEDA</v>
       </c>
       <c r="B23">
-        <v>6603</v>
+        <v>6605</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>GP DONGFENG DF6-RXDL-60</v>
+        <v>GP CHANGAN RRDF-75 L LOBOS</v>
       </c>
       <c r="B24">
-        <v>6607</v>
+        <v>6603</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>GP FOTON G7 TSVS-96</v>
+        <v>GP DONGFENG DF6-RXDL-60</v>
       </c>
       <c r="B25">
-        <v>6602</v>
+        <v>6607</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>GP TM5 TRRD-32 V PIZARRO</v>
+        <v>GP FOTON G7 TSVS-96</v>
       </c>
       <c r="B26">
-        <v>6612</v>
+        <v>6602</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>GP TM5 TSDK-95 L MUNOZ</v>
+        <v>GP TM5 TRRD-32 V PIZARRO</v>
       </c>
       <c r="B27">
-        <v>6599</v>
+        <v>6612</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>GV FOSERO SJHW-18 V OLIVARES</v>
+        <v>GP TM5 TSDK-95 L MUNOZ</v>
       </c>
       <c r="B28">
-        <v>6592</v>
+        <v>6599</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1295,10 +1295,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>GV PEUGEOT THJY-73 J PONCE</v>
+        <v>GV FOSERO SJHW-18 V OLIVARES</v>
       </c>
       <c r="B29">
-        <v>6595</v>
+        <v>6592</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1309,10 +1309,10 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>GV SHDV-50 C CARDENAS</v>
+        <v>GV PEUGEOT THJY-73 J PONCE</v>
       </c>
       <c r="B30">
-        <v>6585</v>
+        <v>6595</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1323,10 +1323,10 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>GV SHLC-74 B MIRANDA</v>
+        <v>GV SHDV-50 C CARDENAS</v>
       </c>
       <c r="B31">
-        <v>6588</v>
+        <v>6585</v>
       </c>
       <c r="C31">
         <v>1</v>

--- a/latest-events.xlsx
+++ b/latest-events.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -422,7 +422,7 @@
         <v>6618</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-09-21 08:46:44</v>
+        <v>2026-09-28 08:44:57</v>
       </c>
       <c r="D2" t="str">
         <v>NO</v>
@@ -436,7 +436,7 @@
         <v>6617</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-09-22 13:42:24</v>
+        <v>2026-09-28 11:51:16</v>
       </c>
       <c r="D3" t="str">
         <v>NO</v>
@@ -450,7 +450,7 @@
         <v>6616</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-09-21 10:02:14</v>
+        <v>2026-09-28 09:36:31</v>
       </c>
       <c r="D4" t="str">
         <v>NO</v>
@@ -458,13 +458,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>GC TM5-RXXG-13 D SILVA</v>
+        <v>GC RXDL-59 OPERACIONES</v>
       </c>
       <c r="B5">
-        <v>6608</v>
+        <v>6581</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-09-21 08:45:35</v>
+        <v>2026-09-30 14:46:46</v>
       </c>
       <c r="D5" t="str">
         <v>NO</v>
@@ -472,13 +472,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>GC TM5-VKFB-85 M CASTRO</v>
+        <v>GC TM5-RXXG-13 D SILVA</v>
       </c>
       <c r="B6">
-        <v>6609</v>
+        <v>6608</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-09-21 10:18:47</v>
+        <v>2026-09-28 09:14:37</v>
       </c>
       <c r="D6" t="str">
         <v>NO</v>
@@ -486,13 +486,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>GC TM5-VRVJ-20 L SALINAS</v>
+        <v>GC TM5-VKFB-85 M CASTRO</v>
       </c>
       <c r="B7">
-        <v>6620</v>
+        <v>6609</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-09-21 11:21:23</v>
+        <v>2026-09-28 10:17:25</v>
       </c>
       <c r="D7" t="str">
         <v>NO</v>
@@ -500,13 +500,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>GC TSVS-89 M AEDO</v>
+        <v>GC TM5-VRVJ-20 L SALINAS</v>
       </c>
       <c r="B8">
-        <v>6610</v>
+        <v>6620</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-09-21 10:34:55</v>
+        <v>2026-09-29 12:22:01</v>
       </c>
       <c r="D8" t="str">
         <v>NO</v>
@@ -514,13 +514,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>GLP ALJIBE SJHW-20</v>
+        <v>GC TSVS-89 M AEDO</v>
       </c>
       <c r="B9">
-        <v>6583</v>
+        <v>6610</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-09-21 14:26:41</v>
+        <v>2026-09-28 09:25:58</v>
       </c>
       <c r="D9" t="str">
         <v>NO</v>
@@ -528,13 +528,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
+        <v>GLP ALJIBE SJHW-20</v>
       </c>
       <c r="B10">
-        <v>6593</v>
+        <v>6583</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-09-21 11:35:08</v>
+        <v>2026-09-29 13:29:44</v>
       </c>
       <c r="D10" t="str">
         <v>NO</v>
@@ -542,27 +542,27 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
+        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
       </c>
       <c r="B11">
-        <v>6597</v>
+        <v>6593</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-09-21 06:00:45</v>
+        <v>2026-09-28 11:37:21</v>
       </c>
       <c r="D11" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>GLP SHDV-51 J REBOLLEDO</v>
+        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
       </c>
       <c r="B12">
-        <v>6598</v>
+        <v>6597</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-09-21 10:00:02</v>
+        <v>2026-09-28 09:49:27</v>
       </c>
       <c r="D12" t="str">
         <v>NO</v>
@@ -570,13 +570,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>GLP SHLC-75 L FONSECA</v>
+        <v>GLP SHDV-51 J REBOLLEDO</v>
       </c>
       <c r="B13">
-        <v>6586</v>
+        <v>6598</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-09-21 11:00:02</v>
+        <v>2026-09-28 09:51:43</v>
       </c>
       <c r="D13" t="str">
         <v>NO</v>
@@ -584,13 +584,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>GLP SHXP-98 CAMION PLUMA</v>
+        <v>GLP SHLC-75 L FONSECA</v>
       </c>
       <c r="B14">
-        <v>6604</v>
+        <v>6586</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-09-21 18:44:12</v>
+        <v>2026-09-28 11:02:22</v>
       </c>
       <c r="D14" t="str">
         <v>NO</v>
@@ -598,13 +598,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>GLP SHXP-99 ALZA HOMBRE</v>
+        <v>GLP SHXP-98 CAMION PLUMA</v>
       </c>
       <c r="B15">
-        <v>6601</v>
+        <v>6604</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-09-21 12:41:35</v>
+        <v>2026-09-28 13:17:14</v>
       </c>
       <c r="D15" t="str">
         <v>NO</v>
@@ -612,13 +612,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>GLP SKDX-44 V VIAL</v>
+        <v>GLP SHXP-99 ALZA HOMBRE</v>
       </c>
       <c r="B16">
-        <v>6606</v>
+        <v>6601</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-09-21 11:50:45</v>
+        <v>2026-09-28 13:04:21</v>
       </c>
       <c r="D16" t="str">
         <v>NO</v>
@@ -626,13 +626,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>GLP SSZD-71  J VALLEJOS</v>
+        <v>GLP SKDX-44 V VIAL</v>
       </c>
       <c r="B17">
-        <v>6580</v>
+        <v>6606</v>
       </c>
       <c r="C17" t="str">
-        <v>2026-09-21 10:58:18</v>
+        <v>2026-09-28 13:15:17</v>
       </c>
       <c r="D17" t="str">
         <v>NO</v>
@@ -640,27 +640,27 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
+        <v>GLP SSZD-71  J VALLEJOS</v>
       </c>
       <c r="B18">
-        <v>6594</v>
+        <v>6580</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-09-21 12:25:25</v>
+        <v>2026-09-28 20:52:38</v>
       </c>
       <c r="D18" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>GP -SHLC-76 F SEPULVEDA</v>
+        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
       </c>
       <c r="B19">
-        <v>6605</v>
+        <v>6594</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-09-21 12:37:55</v>
+        <v>2026-09-28 10:54:39</v>
       </c>
       <c r="D19" t="str">
         <v>NO</v>
@@ -668,13 +668,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>GP CHANGAN RRDF-75 L LOBOS</v>
+        <v>GP -SHLC-76 F SEPULVEDA</v>
       </c>
       <c r="B20">
-        <v>6603</v>
+        <v>6605</v>
       </c>
       <c r="C20" t="str">
-        <v>2026-09-21 12:47:19</v>
+        <v>2026-09-28 10:53:38</v>
       </c>
       <c r="D20" t="str">
         <v>NO</v>
@@ -682,13 +682,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>GP DONGFENG DF6-RXDL-60</v>
+        <v>GP CHANGAN RRDF-75 L LOBOS</v>
       </c>
       <c r="B21">
-        <v>6607</v>
+        <v>6603</v>
       </c>
       <c r="C21" t="str">
-        <v>2026-09-21 09:47:05</v>
+        <v>2026-09-28 09:28:11</v>
       </c>
       <c r="D21" t="str">
         <v>NO</v>
@@ -696,13 +696,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>GP FOTON G7 TSVS-96</v>
+        <v>GP DONGFENG DF6-RXDL-60</v>
       </c>
       <c r="B22">
-        <v>6602</v>
+        <v>6607</v>
       </c>
       <c r="C22" t="str">
-        <v>2026-09-21 11:50:34</v>
+        <v>2026-09-28 12:01:39</v>
       </c>
       <c r="D22" t="str">
         <v>NO</v>
@@ -710,13 +710,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>GP TM5 TRRD-32 V PIZARRO</v>
+        <v>GP FOTON G7 TSVS-96</v>
       </c>
       <c r="B23">
-        <v>6612</v>
+        <v>6602</v>
       </c>
       <c r="C23" t="str">
-        <v>2026-09-21 10:19:47</v>
+        <v>2026-09-28 10:10:34</v>
       </c>
       <c r="D23" t="str">
         <v>NO</v>
@@ -724,13 +724,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>GP TM5 TSDK-95 L MUNOZ</v>
+        <v>GP TM5 TRRD-32 V PIZARRO</v>
       </c>
       <c r="B24">
-        <v>6599</v>
+        <v>6612</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-09-21 11:30:04</v>
+        <v>2026-09-28 10:52:21</v>
       </c>
       <c r="D24" t="str">
         <v>NO</v>
@@ -738,27 +738,27 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>GV FORD BU-9781 V OLIVARES</v>
+        <v>GP TM5 TSDK-95 L MUNOZ</v>
       </c>
       <c r="B25">
-        <v>6621</v>
+        <v>6599</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-09-22 20:57:49</v>
+        <v>2026-09-28 10:52:15</v>
       </c>
       <c r="D25" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>GV FOSERO SJHW-18 V OLIVARES</v>
+        <v>GV FORD BU-9781 V OLIVARES</v>
       </c>
       <c r="B26">
-        <v>6592</v>
+        <v>6621</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-09-21 07:33:19</v>
+        <v>2026-09-29 11:14:00</v>
       </c>
       <c r="D26" t="str">
         <v>NO</v>
@@ -766,13 +766,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>GV PEUGEOT THJY-73 J PONCE</v>
+        <v>GV FOSERO SJHW-18 V OLIVARES</v>
       </c>
       <c r="B27">
-        <v>6595</v>
+        <v>6592</v>
       </c>
       <c r="C27" t="str">
-        <v>2026-09-21 09:57:24</v>
+        <v>2026-09-28 07:21:27</v>
       </c>
       <c r="D27" t="str">
         <v>NO</v>
@@ -780,13 +780,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>GV SHDV-50 C CARDENAS</v>
+        <v>GV PEUGEOT THJY-73 J PONCE</v>
       </c>
       <c r="B28">
-        <v>6585</v>
+        <v>6595</v>
       </c>
       <c r="C28" t="str">
-        <v>2026-09-21 10:36:40</v>
+        <v>2026-09-28 09:56:32</v>
       </c>
       <c r="D28" t="str">
         <v>NO</v>
@@ -794,27 +794,27 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>GV SHLC-74 B MIRANDA</v>
+        <v>GV SHDV-50 C CARDENAS</v>
       </c>
       <c r="B29">
-        <v>6588</v>
+        <v>6585</v>
       </c>
       <c r="C29" t="str">
-        <v>2026-09-21 20:51:22</v>
+        <v>2026-09-28 10:10:56</v>
       </c>
       <c r="D29" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>GV TDKV-88 L CORDERO</v>
+        <v>GV SHLC-74 B MIRANDA</v>
       </c>
       <c r="B30">
-        <v>6587</v>
+        <v>6588</v>
       </c>
       <c r="C30" t="str">
-        <v>2026-09-21 10:25:11</v>
+        <v>2026-09-28 11:59:24</v>
       </c>
       <c r="D30" t="str">
         <v>NO</v>
@@ -822,13 +822,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>GV TDLD-98 J PACHECHO</v>
+        <v>GV TDKV-88 L CORDERO</v>
       </c>
       <c r="B31">
-        <v>6582</v>
+        <v>6587</v>
       </c>
       <c r="C31" t="str">
-        <v>2026-09-21 11:04:25</v>
+        <v>2026-09-28 10:23:55</v>
       </c>
       <c r="D31" t="str">
         <v>NO</v>
@@ -836,70 +836,84 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>GV TM5 RXXG-15 E CABANILLA</v>
+        <v>GV TDLD-98 J PACHECHO</v>
       </c>
       <c r="B32">
-        <v>6589</v>
+        <v>6582</v>
       </c>
       <c r="C32" t="str">
-        <v>2026-09-21 20:10:54</v>
+        <v>2026-09-28 11:00:49</v>
       </c>
       <c r="D32" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>GV TM5 TDLD-46 M MARTINEZ</v>
+        <v>GV TM5 RXXG-15 E CABANILLA</v>
       </c>
       <c r="B33">
-        <v>6596</v>
+        <v>6589</v>
       </c>
       <c r="C33" t="str">
-        <v>2026-09-21 11:03:31</v>
+        <v>2026-09-28 20:04:44</v>
       </c>
       <c r="D33" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>GV TOLVA SPGW-29 V OLIVARES</v>
+        <v>GV TM5 TDLD-46 M MARTINEZ</v>
       </c>
       <c r="B34">
-        <v>6619</v>
+        <v>6596</v>
       </c>
       <c r="C34" t="str">
-        <v>2026-09-21 20:30:53</v>
+        <v>2026-09-28 11:05:35</v>
       </c>
       <c r="D34" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
+        <v>GV TOLVA SPGW-29 V OLIVARES</v>
+      </c>
+      <c r="B35">
+        <v>6619</v>
+      </c>
+      <c r="C35" t="str">
+        <v>2026-09-28 19:08:08</v>
+      </c>
+      <c r="D35" t="str">
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
         <v>JAC  LYTS-17 G GALEA</v>
       </c>
-      <c r="B35">
+      <c r="B36">
         <v>6614</v>
       </c>
-      <c r="C35" t="str">
-        <v>2026-09-21 08:47:52</v>
-      </c>
-      <c r="D35" t="str">
+      <c r="C36" t="str">
+        <v>2026-09-28 08:45:01</v>
+      </c>
+      <c r="D36" t="str">
         <v>NO</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D36"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -917,10 +931,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
+        <v>GLP SSZD-71  J VALLEJOS</v>
       </c>
       <c r="B2">
-        <v>6597</v>
+        <v>6580</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -931,10 +945,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>GV FORD BU-9781 V OLIVARES</v>
+        <v>GV TM5 RXXG-15 E CABANILLA</v>
       </c>
       <c r="B3">
-        <v>6621</v>
+        <v>6589</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -945,10 +959,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>GV SHLC-74 B MIRANDA</v>
+        <v>GV TOLVA SPGW-29 V OLIVARES</v>
       </c>
       <c r="B4">
-        <v>6588</v>
+        <v>6619</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -959,38 +973,38 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>GV TM5 RXXG-15 E CABANILLA</v>
+        <v>DONGFENG DF6 SRSR-97</v>
       </c>
       <c r="B5">
-        <v>6589</v>
+        <v>6618</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>GV TOLVA SPGW-29 V OLIVARES</v>
+        <v>GC MAXUS PCRF-25 TERRENO</v>
       </c>
       <c r="B6">
-        <v>6619</v>
+        <v>6617</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>DONGFENG DF6 SRSR-97</v>
+        <v>GC MAXUS PKFF-65 G VICENCIO</v>
       </c>
       <c r="B7">
-        <v>6618</v>
+        <v>6616</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1001,10 +1015,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>GC MAXUS PCRF-25 TERRENO</v>
+        <v>GC RXDL-59 OPERACIONES</v>
       </c>
       <c r="B8">
-        <v>6617</v>
+        <v>6581</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1015,10 +1029,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>GC MAXUS PKFF-65 G VICENCIO</v>
+        <v>GC TM5-RXXG-13 D SILVA</v>
       </c>
       <c r="B9">
-        <v>6616</v>
+        <v>6608</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1029,10 +1043,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>GC TM5-RXXG-13 D SILVA</v>
+        <v>GC TM5-VKFB-85 M CASTRO</v>
       </c>
       <c r="B10">
-        <v>6608</v>
+        <v>6609</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1043,10 +1057,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>GC TM5-VKFB-85 M CASTRO</v>
+        <v>GC TM5-VRVJ-20 L SALINAS</v>
       </c>
       <c r="B11">
-        <v>6609</v>
+        <v>6620</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1057,10 +1071,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>GC TM5-VRVJ-20 L SALINAS</v>
+        <v>GC TSVS-89 M AEDO</v>
       </c>
       <c r="B12">
-        <v>6620</v>
+        <v>6610</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1071,10 +1085,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>GC TSVS-89 M AEDO</v>
+        <v>GLP ALJIBE SJHW-20</v>
       </c>
       <c r="B13">
-        <v>6610</v>
+        <v>6583</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1085,10 +1099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>GLP ALJIBE SJHW-20</v>
+        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
       </c>
       <c r="B14">
-        <v>6583</v>
+        <v>6593</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1099,10 +1113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
+        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
       </c>
       <c r="B15">
-        <v>6593</v>
+        <v>6597</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1183,10 +1197,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>GLP SSZD-71  J VALLEJOS</v>
+        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
       </c>
       <c r="B21">
-        <v>6580</v>
+        <v>6594</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1197,10 +1211,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
+        <v>GP -SHLC-76 F SEPULVEDA</v>
       </c>
       <c r="B22">
-        <v>6594</v>
+        <v>6605</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1211,10 +1225,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>GP -SHLC-76 F SEPULVEDA</v>
+        <v>GP CHANGAN RRDF-75 L LOBOS</v>
       </c>
       <c r="B23">
-        <v>6605</v>
+        <v>6603</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1225,10 +1239,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>GP CHANGAN RRDF-75 L LOBOS</v>
+        <v>GP DONGFENG DF6-RXDL-60</v>
       </c>
       <c r="B24">
-        <v>6603</v>
+        <v>6607</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1239,10 +1253,10 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>GP DONGFENG DF6-RXDL-60</v>
+        <v>GP FOTON G7 TSVS-96</v>
       </c>
       <c r="B25">
-        <v>6607</v>
+        <v>6602</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1253,10 +1267,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>GP FOTON G7 TSVS-96</v>
+        <v>GP TM5 TRRD-32 V PIZARRO</v>
       </c>
       <c r="B26">
-        <v>6602</v>
+        <v>6612</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1267,10 +1281,10 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>GP TM5 TRRD-32 V PIZARRO</v>
+        <v>GP TM5 TSDK-95 L MUNOZ</v>
       </c>
       <c r="B27">
-        <v>6612</v>
+        <v>6599</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1281,10 +1295,10 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>GP TM5 TSDK-95 L MUNOZ</v>
+        <v>GV FORD BU-9781 V OLIVARES</v>
       </c>
       <c r="B28">
-        <v>6599</v>
+        <v>6621</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1337,10 +1351,10 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>GV TDKV-88 L CORDERO</v>
+        <v>GV SHLC-74 B MIRANDA</v>
       </c>
       <c r="B32">
-        <v>6587</v>
+        <v>6588</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1351,10 +1365,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>GV TDLD-98 J PACHECHO</v>
+        <v>GV TDKV-88 L CORDERO</v>
       </c>
       <c r="B33">
-        <v>6582</v>
+        <v>6587</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1365,10 +1379,10 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>GV TM5 TDLD-46 M MARTINEZ</v>
+        <v>GV TDLD-98 J PACHECHO</v>
       </c>
       <c r="B34">
-        <v>6596</v>
+        <v>6582</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -1379,21 +1393,35 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
+        <v>GV TM5 TDLD-46 M MARTINEZ</v>
+      </c>
+      <c r="B35">
+        <v>6596</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
         <v>JAC  LYTS-17 G GALEA</v>
       </c>
-      <c r="B35">
+      <c r="B36">
         <v>6614</v>
       </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D36"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/latest-events.xlsx
+++ b/latest-events.xlsx
@@ -422,7 +422,7 @@
         <v>6618</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-09-28 08:44:57</v>
+        <v>2026-10-05 08:49:24</v>
       </c>
       <c r="D2" t="str">
         <v>NO</v>
@@ -436,7 +436,7 @@
         <v>6617</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-09-28 11:51:16</v>
+        <v>2026-10-05 12:47:06</v>
       </c>
       <c r="D3" t="str">
         <v>NO</v>
@@ -450,7 +450,7 @@
         <v>6616</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-09-28 09:36:31</v>
+        <v>2026-10-05 09:32:57</v>
       </c>
       <c r="D4" t="str">
         <v>NO</v>
@@ -464,10 +464,10 @@
         <v>6581</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-09-30 14:46:46</v>
+        <v>2026-10-05 20:11:24</v>
       </c>
       <c r="D5" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="6">
@@ -478,7 +478,7 @@
         <v>6608</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-09-28 09:14:37</v>
+        <v>2026-10-05 09:16:41</v>
       </c>
       <c r="D6" t="str">
         <v>NO</v>
@@ -492,7 +492,7 @@
         <v>6609</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-09-28 10:17:25</v>
+        <v>2026-10-05 10:26:10</v>
       </c>
       <c r="D7" t="str">
         <v>NO</v>
@@ -506,7 +506,7 @@
         <v>6620</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-09-29 12:22:01</v>
+        <v>2026-10-05 09:45:16</v>
       </c>
       <c r="D8" t="str">
         <v>NO</v>
@@ -520,7 +520,7 @@
         <v>6610</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-09-28 09:25:58</v>
+        <v>2026-10-07 18:26:41</v>
       </c>
       <c r="D9" t="str">
         <v>NO</v>
@@ -534,7 +534,7 @@
         <v>6583</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-09-29 13:29:44</v>
+        <v>2026-10-05 13:45:12</v>
       </c>
       <c r="D10" t="str">
         <v>NO</v>
@@ -548,7 +548,7 @@
         <v>6593</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-09-28 11:37:21</v>
+        <v>2026-10-05 10:07:07</v>
       </c>
       <c r="D11" t="str">
         <v>NO</v>
@@ -562,7 +562,7 @@
         <v>6597</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-09-28 09:49:27</v>
+        <v>2026-10-05 08:36:27</v>
       </c>
       <c r="D12" t="str">
         <v>NO</v>
@@ -576,7 +576,7 @@
         <v>6598</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-09-28 09:51:43</v>
+        <v>2026-10-05 09:49:53</v>
       </c>
       <c r="D13" t="str">
         <v>NO</v>
@@ -590,7 +590,7 @@
         <v>6586</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-09-28 11:02:22</v>
+        <v>2026-10-05 10:51:33</v>
       </c>
       <c r="D14" t="str">
         <v>NO</v>
@@ -604,7 +604,7 @@
         <v>6604</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-09-28 13:17:14</v>
+        <v>2026-10-05 18:14:06</v>
       </c>
       <c r="D15" t="str">
         <v>NO</v>
@@ -618,7 +618,7 @@
         <v>6601</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-09-28 13:04:21</v>
+        <v>2026-10-05 13:50:53</v>
       </c>
       <c r="D16" t="str">
         <v>NO</v>
@@ -632,10 +632,10 @@
         <v>6606</v>
       </c>
       <c r="C17" t="str">
-        <v>2026-09-28 13:15:17</v>
+        <v>2026-10-05 04:05:33</v>
       </c>
       <c r="D17" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="18">
@@ -646,10 +646,10 @@
         <v>6580</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-09-28 20:52:38</v>
+        <v>2026-10-07 13:00:58</v>
       </c>
       <c r="D18" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="19">
@@ -660,7 +660,7 @@
         <v>6594</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-09-28 10:54:39</v>
+        <v>2026-10-05 11:05:03</v>
       </c>
       <c r="D19" t="str">
         <v>NO</v>
@@ -674,7 +674,7 @@
         <v>6605</v>
       </c>
       <c r="C20" t="str">
-        <v>2026-09-28 10:53:38</v>
+        <v>2026-10-05 10:55:29</v>
       </c>
       <c r="D20" t="str">
         <v>NO</v>
@@ -688,7 +688,7 @@
         <v>6603</v>
       </c>
       <c r="C21" t="str">
-        <v>2026-09-28 09:28:11</v>
+        <v>2026-10-05 10:15:20</v>
       </c>
       <c r="D21" t="str">
         <v>NO</v>
@@ -702,7 +702,7 @@
         <v>6607</v>
       </c>
       <c r="C22" t="str">
-        <v>2026-09-28 12:01:39</v>
+        <v>2026-10-05 09:39:13</v>
       </c>
       <c r="D22" t="str">
         <v>NO</v>
@@ -716,7 +716,7 @@
         <v>6602</v>
       </c>
       <c r="C23" t="str">
-        <v>2026-09-28 10:10:34</v>
+        <v>2026-10-05 10:06:04</v>
       </c>
       <c r="D23" t="str">
         <v>NO</v>
@@ -730,7 +730,7 @@
         <v>6612</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-09-28 10:52:21</v>
+        <v>2026-10-05 10:56:56</v>
       </c>
       <c r="D24" t="str">
         <v>NO</v>
@@ -744,7 +744,7 @@
         <v>6599</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-09-28 10:52:15</v>
+        <v>2026-10-05 10:54:43</v>
       </c>
       <c r="D25" t="str">
         <v>NO</v>
@@ -758,7 +758,7 @@
         <v>6621</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-09-29 11:14:00</v>
+        <v>2026-10-06 11:15:12</v>
       </c>
       <c r="D26" t="str">
         <v>NO</v>
@@ -772,7 +772,7 @@
         <v>6592</v>
       </c>
       <c r="C27" t="str">
-        <v>2026-09-28 07:21:27</v>
+        <v>2026-10-05 07:08:56</v>
       </c>
       <c r="D27" t="str">
         <v>NO</v>
@@ -786,7 +786,7 @@
         <v>6595</v>
       </c>
       <c r="C28" t="str">
-        <v>2026-09-28 09:56:32</v>
+        <v>2026-10-05 10:03:57</v>
       </c>
       <c r="D28" t="str">
         <v>NO</v>
@@ -800,7 +800,7 @@
         <v>6585</v>
       </c>
       <c r="C29" t="str">
-        <v>2026-09-28 10:10:56</v>
+        <v>2026-10-05 10:09:45</v>
       </c>
       <c r="D29" t="str">
         <v>NO</v>
@@ -814,7 +814,7 @@
         <v>6588</v>
       </c>
       <c r="C30" t="str">
-        <v>2026-09-28 11:59:24</v>
+        <v>2026-10-05 11:00:59</v>
       </c>
       <c r="D30" t="str">
         <v>NO</v>
@@ -828,7 +828,7 @@
         <v>6587</v>
       </c>
       <c r="C31" t="str">
-        <v>2026-09-28 10:23:55</v>
+        <v>2026-10-05 10:30:06</v>
       </c>
       <c r="D31" t="str">
         <v>NO</v>
@@ -842,7 +842,7 @@
         <v>6582</v>
       </c>
       <c r="C32" t="str">
-        <v>2026-09-28 11:00:49</v>
+        <v>2026-10-05 11:13:07</v>
       </c>
       <c r="D32" t="str">
         <v>NO</v>
@@ -856,7 +856,7 @@
         <v>6589</v>
       </c>
       <c r="C33" t="str">
-        <v>2026-09-28 20:04:44</v>
+        <v>2026-10-05 20:09:55</v>
       </c>
       <c r="D33" t="str">
         <v>SI</v>
@@ -870,7 +870,7 @@
         <v>6596</v>
       </c>
       <c r="C34" t="str">
-        <v>2026-09-28 11:05:35</v>
+        <v>2026-10-05 11:06:39</v>
       </c>
       <c r="D34" t="str">
         <v>NO</v>
@@ -884,7 +884,7 @@
         <v>6619</v>
       </c>
       <c r="C35" t="str">
-        <v>2026-09-28 19:08:08</v>
+        <v>2026-10-05 20:08:53</v>
       </c>
       <c r="D35" t="str">
         <v>SI</v>
@@ -898,7 +898,7 @@
         <v>6614</v>
       </c>
       <c r="C36" t="str">
-        <v>2026-09-28 08:45:01</v>
+        <v>2026-10-05 08:50:59</v>
       </c>
       <c r="D36" t="str">
         <v>NO</v>
@@ -931,10 +931,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>GLP SSZD-71  J VALLEJOS</v>
+        <v>GC RXDL-59 OPERACIONES</v>
       </c>
       <c r="B2">
-        <v>6580</v>
+        <v>6581</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -945,10 +945,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>GV TM5 RXXG-15 E CABANILLA</v>
+        <v>GLP SKDX-44 V VIAL</v>
       </c>
       <c r="B3">
-        <v>6589</v>
+        <v>6606</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -959,10 +959,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>GV TOLVA SPGW-29 V OLIVARES</v>
+        <v>GV TM5 RXXG-15 E CABANILLA</v>
       </c>
       <c r="B4">
-        <v>6619</v>
+        <v>6589</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -973,24 +973,24 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>DONGFENG DF6 SRSR-97</v>
+        <v>GV TOLVA SPGW-29 V OLIVARES</v>
       </c>
       <c r="B5">
-        <v>6618</v>
+        <v>6619</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>GC MAXUS PCRF-25 TERRENO</v>
+        <v>DONGFENG DF6 SRSR-97</v>
       </c>
       <c r="B6">
-        <v>6617</v>
+        <v>6618</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>GC MAXUS PKFF-65 G VICENCIO</v>
+        <v>GC MAXUS PCRF-25 TERRENO</v>
       </c>
       <c r="B7">
-        <v>6616</v>
+        <v>6617</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>GC RXDL-59 OPERACIONES</v>
+        <v>GC MAXUS PKFF-65 G VICENCIO</v>
       </c>
       <c r="B8">
-        <v>6581</v>
+        <v>6616</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>GLP SKDX-44 V VIAL</v>
+        <v>GLP SSZD-71  J VALLEJOS</v>
       </c>
       <c r="B20">
-        <v>6606</v>
+        <v>6580</v>
       </c>
       <c r="C20">
         <v>1</v>

--- a/latest-events.xlsx
+++ b/latest-events.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D33"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -422,7 +422,7 @@
         <v>6618</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-10-05 08:49:24</v>
+        <v>2026-10-13 08:47:03</v>
       </c>
       <c r="D2" t="str">
         <v>NO</v>
@@ -436,7 +436,7 @@
         <v>6617</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-10-05 12:47:06</v>
+        <v>2026-10-14 17:43:07</v>
       </c>
       <c r="D3" t="str">
         <v>NO</v>
@@ -450,7 +450,7 @@
         <v>6616</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-10-05 09:32:57</v>
+        <v>2026-10-12 09:44:37</v>
       </c>
       <c r="D4" t="str">
         <v>NO</v>
@@ -458,13 +458,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>GC RXDL-59 OPERACIONES</v>
+        <v>GC TM5-RXXG-13 D SILVA</v>
       </c>
       <c r="B5">
-        <v>6581</v>
+        <v>6608</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-10-05 20:11:24</v>
+        <v>2026-10-12 21:34:09</v>
       </c>
       <c r="D5" t="str">
         <v>SI</v>
@@ -472,13 +472,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>GC TM5-RXXG-13 D SILVA</v>
+        <v>GC TM5-VKFB-85 M CASTRO</v>
       </c>
       <c r="B6">
-        <v>6608</v>
+        <v>6609</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-10-05 09:16:41</v>
+        <v>2026-10-13 10:19:11</v>
       </c>
       <c r="D6" t="str">
         <v>NO</v>
@@ -486,13 +486,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>GC TM5-VKFB-85 M CASTRO</v>
+        <v>GC TM5-VRVJ-20 L SALINAS</v>
       </c>
       <c r="B7">
-        <v>6609</v>
+        <v>6620</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-10-05 10:26:10</v>
+        <v>2026-10-13 11:14:46</v>
       </c>
       <c r="D7" t="str">
         <v>NO</v>
@@ -500,27 +500,27 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>GC TM5-VRVJ-20 L SALINAS</v>
+        <v>GLP ALJIBE SJHW-20</v>
       </c>
       <c r="B8">
-        <v>6620</v>
+        <v>6583</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-10-05 09:45:16</v>
+        <v>2026-10-14 03:11:25</v>
       </c>
       <c r="D8" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>GC TSVS-89 M AEDO</v>
+        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
       </c>
       <c r="B9">
-        <v>6610</v>
+        <v>6593</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-10-07 18:26:41</v>
+        <v>2026-10-12 15:41:34</v>
       </c>
       <c r="D9" t="str">
         <v>NO</v>
@@ -528,13 +528,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>GLP ALJIBE SJHW-20</v>
+        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
       </c>
       <c r="B10">
-        <v>6583</v>
+        <v>6597</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-10-05 13:45:12</v>
+        <v>2026-10-12 10:24:35</v>
       </c>
       <c r="D10" t="str">
         <v>NO</v>
@@ -542,13 +542,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
+        <v>GLP SHDV-51 J REBOLLEDO</v>
       </c>
       <c r="B11">
-        <v>6593</v>
+        <v>6598</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-10-05 10:07:07</v>
+        <v>2026-10-12 15:25:43</v>
       </c>
       <c r="D11" t="str">
         <v>NO</v>
@@ -556,27 +556,27 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
+        <v>GLP SHLC-75 L FONSECA</v>
       </c>
       <c r="B12">
-        <v>6597</v>
+        <v>6586</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-10-05 08:36:27</v>
+        <v>2026-10-13 20:51:31</v>
       </c>
       <c r="D12" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>GLP SHDV-51 J REBOLLEDO</v>
+        <v>GLP SHXP-98 CAMION PLUMA</v>
       </c>
       <c r="B13">
-        <v>6598</v>
+        <v>6604</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-10-05 09:49:53</v>
+        <v>2026-10-14 14:36:05</v>
       </c>
       <c r="D13" t="str">
         <v>NO</v>
@@ -584,13 +584,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>GLP SHLC-75 L FONSECA</v>
+        <v>GLP SHXP-99 ALZA HOMBRE</v>
       </c>
       <c r="B14">
-        <v>6586</v>
+        <v>6601</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-10-05 10:51:33</v>
+        <v>2026-10-14 13:51:40</v>
       </c>
       <c r="D14" t="str">
         <v>NO</v>
@@ -598,27 +598,27 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>GLP SHXP-98 CAMION PLUMA</v>
+        <v>GLP SKDX-44 V VIAL</v>
       </c>
       <c r="B15">
-        <v>6604</v>
+        <v>6606</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-10-05 18:14:06</v>
+        <v>2026-10-12 04:00:20</v>
       </c>
       <c r="D15" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>GLP SHXP-99 ALZA HOMBRE</v>
+        <v>GLP SSZD-71  J VALLEJOS</v>
       </c>
       <c r="B16">
-        <v>6601</v>
+        <v>6580</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-10-05 13:50:53</v>
+        <v>2026-10-13 12:17:08</v>
       </c>
       <c r="D16" t="str">
         <v>NO</v>
@@ -626,27 +626,27 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>GLP SKDX-44 V VIAL</v>
+        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
       </c>
       <c r="B17">
-        <v>6606</v>
+        <v>6594</v>
       </c>
       <c r="C17" t="str">
-        <v>2026-10-05 04:05:33</v>
+        <v>2026-10-13 11:04:07</v>
       </c>
       <c r="D17" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>GLP SSZD-71  J VALLEJOS</v>
+        <v>GP -SHLC-76 F SEPULVEDA</v>
       </c>
       <c r="B18">
-        <v>6580</v>
+        <v>6605</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-10-07 13:00:58</v>
+        <v>2026-10-13 11:07:11</v>
       </c>
       <c r="D18" t="str">
         <v>NO</v>
@@ -654,13 +654,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
+        <v>GP CHANGAN RRDF-75 L LOBOS</v>
       </c>
       <c r="B19">
-        <v>6594</v>
+        <v>6603</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-10-05 11:05:03</v>
+        <v>2026-10-13 09:56:59</v>
       </c>
       <c r="D19" t="str">
         <v>NO</v>
@@ -668,27 +668,27 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>GP -SHLC-76 F SEPULVEDA</v>
+        <v>GP DONGFENG DF6-RXDL-60</v>
       </c>
       <c r="B20">
-        <v>6605</v>
+        <v>6607</v>
       </c>
       <c r="C20" t="str">
-        <v>2026-10-05 10:55:29</v>
+        <v>2026-10-12 05:33:27</v>
       </c>
       <c r="D20" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>GP CHANGAN RRDF-75 L LOBOS</v>
+        <v>GP FOTON G7 TSVS-96</v>
       </c>
       <c r="B21">
-        <v>6603</v>
+        <v>6602</v>
       </c>
       <c r="C21" t="str">
-        <v>2026-10-05 10:15:20</v>
+        <v>2026-10-13 14:11:34</v>
       </c>
       <c r="D21" t="str">
         <v>NO</v>
@@ -696,13 +696,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>GP DONGFENG DF6-RXDL-60</v>
+        <v>GP TM5 TRRD-32 V PIZARRO</v>
       </c>
       <c r="B22">
-        <v>6607</v>
+        <v>6612</v>
       </c>
       <c r="C22" t="str">
-        <v>2026-10-05 09:39:13</v>
+        <v>2026-10-13 11:09:46</v>
       </c>
       <c r="D22" t="str">
         <v>NO</v>
@@ -710,13 +710,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>GP FOTON G7 TSVS-96</v>
+        <v>GP TM5 TSDK-95 L MUNOZ</v>
       </c>
       <c r="B23">
-        <v>6602</v>
+        <v>6599</v>
       </c>
       <c r="C23" t="str">
-        <v>2026-10-05 10:06:04</v>
+        <v>2026-10-13 10:49:25</v>
       </c>
       <c r="D23" t="str">
         <v>NO</v>
@@ -724,13 +724,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>GP TM5 TRRD-32 V PIZARRO</v>
+        <v>GV FOSERO SJHW-18 V OLIVARES</v>
       </c>
       <c r="B24">
-        <v>6612</v>
+        <v>6592</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-10-05 10:56:56</v>
+        <v>2026-10-13 07:12:16</v>
       </c>
       <c r="D24" t="str">
         <v>NO</v>
@@ -738,13 +738,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>GP TM5 TSDK-95 L MUNOZ</v>
+        <v>GV PEUGEOT THJY-73 J PONCE</v>
       </c>
       <c r="B25">
-        <v>6599</v>
+        <v>6595</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-10-05 10:54:43</v>
+        <v>2026-10-13 10:02:35</v>
       </c>
       <c r="D25" t="str">
         <v>NO</v>
@@ -752,13 +752,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>GV FORD BU-9781 V OLIVARES</v>
+        <v>GV SHDV-50 C CARDENAS</v>
       </c>
       <c r="B26">
-        <v>6621</v>
+        <v>6585</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-10-06 11:15:12</v>
+        <v>2026-10-13 10:17:31</v>
       </c>
       <c r="D26" t="str">
         <v>NO</v>
@@ -766,13 +766,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>GV FOSERO SJHW-18 V OLIVARES</v>
+        <v>GV SHLC-74 B MIRANDA</v>
       </c>
       <c r="B27">
-        <v>6592</v>
+        <v>6588</v>
       </c>
       <c r="C27" t="str">
-        <v>2026-10-05 07:08:56</v>
+        <v>2026-10-13 11:01:56</v>
       </c>
       <c r="D27" t="str">
         <v>NO</v>
@@ -780,13 +780,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>GV PEUGEOT THJY-73 J PONCE</v>
+        <v>GV TDKV-88 L CORDERO</v>
       </c>
       <c r="B28">
-        <v>6595</v>
+        <v>6587</v>
       </c>
       <c r="C28" t="str">
-        <v>2026-10-05 10:03:57</v>
+        <v>2026-10-13 10:24:10</v>
       </c>
       <c r="D28" t="str">
         <v>NO</v>
@@ -794,13 +794,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>GV SHDV-50 C CARDENAS</v>
+        <v>GV TDLD-98 J PACHECHO</v>
       </c>
       <c r="B29">
-        <v>6585</v>
+        <v>6582</v>
       </c>
       <c r="C29" t="str">
-        <v>2026-10-05 10:09:45</v>
+        <v>2026-10-13 14:12:20</v>
       </c>
       <c r="D29" t="str">
         <v>NO</v>
@@ -808,13 +808,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>GV SHLC-74 B MIRANDA</v>
+        <v>GV TM5 RXXG-15 E CABANILLA</v>
       </c>
       <c r="B30">
-        <v>6588</v>
+        <v>6589</v>
       </c>
       <c r="C30" t="str">
-        <v>2026-10-05 11:00:59</v>
+        <v>2026-10-13 12:04:37</v>
       </c>
       <c r="D30" t="str">
         <v>NO</v>
@@ -822,13 +822,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>GV TDKV-88 L CORDERO</v>
+        <v>GV TM5 TDLD-46 M MARTINEZ</v>
       </c>
       <c r="B31">
-        <v>6587</v>
+        <v>6596</v>
       </c>
       <c r="C31" t="str">
-        <v>2026-10-05 10:30:06</v>
+        <v>2026-10-13 11:16:29</v>
       </c>
       <c r="D31" t="str">
         <v>NO</v>
@@ -836,84 +836,42 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>GV TDLD-98 J PACHECHO</v>
+        <v>GV TOLVA SPGW-29 V OLIVARES</v>
       </c>
       <c r="B32">
-        <v>6582</v>
+        <v>6619</v>
       </c>
       <c r="C32" t="str">
-        <v>2026-10-05 11:13:07</v>
+        <v>2026-10-13 20:35:48</v>
       </c>
       <c r="D32" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>GV TM5 RXXG-15 E CABANILLA</v>
+        <v>JAC  LYTS-17 G GALEA</v>
       </c>
       <c r="B33">
-        <v>6589</v>
+        <v>6614</v>
       </c>
       <c r="C33" t="str">
-        <v>2026-10-05 20:09:55</v>
+        <v>2026-10-13 08:47:41</v>
       </c>
       <c r="D33" t="str">
-        <v>SI</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>GV TM5 TDLD-46 M MARTINEZ</v>
-      </c>
-      <c r="B34">
-        <v>6596</v>
-      </c>
-      <c r="C34" t="str">
-        <v>2026-10-05 11:06:39</v>
-      </c>
-      <c r="D34" t="str">
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>GV TOLVA SPGW-29 V OLIVARES</v>
-      </c>
-      <c r="B35">
-        <v>6619</v>
-      </c>
-      <c r="C35" t="str">
-        <v>2026-10-05 20:08:53</v>
-      </c>
-      <c r="D35" t="str">
-        <v>SI</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>JAC  LYTS-17 G GALEA</v>
-      </c>
-      <c r="B36">
-        <v>6614</v>
-      </c>
-      <c r="C36" t="str">
-        <v>2026-10-05 08:50:59</v>
-      </c>
-      <c r="D36" t="str">
         <v>NO</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D33"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D33"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -931,10 +889,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>GC RXDL-59 OPERACIONES</v>
+        <v>GC TM5-RXXG-13 D SILVA</v>
       </c>
       <c r="B2">
-        <v>6581</v>
+        <v>6608</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -945,10 +903,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>GLP SKDX-44 V VIAL</v>
+        <v>GLP ALJIBE SJHW-20</v>
       </c>
       <c r="B3">
-        <v>6606</v>
+        <v>6583</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -959,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>GV TM5 RXXG-15 E CABANILLA</v>
+        <v>GLP SHLC-75 L FONSECA</v>
       </c>
       <c r="B4">
-        <v>6589</v>
+        <v>6586</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -973,10 +931,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>GV TOLVA SPGW-29 V OLIVARES</v>
+        <v>GLP SKDX-44 V VIAL</v>
       </c>
       <c r="B5">
-        <v>6619</v>
+        <v>6606</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -987,38 +945,38 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>DONGFENG DF6 SRSR-97</v>
+        <v>GP DONGFENG DF6-RXDL-60</v>
       </c>
       <c r="B6">
-        <v>6618</v>
+        <v>6607</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>GC MAXUS PCRF-25 TERRENO</v>
+        <v>GV TOLVA SPGW-29 V OLIVARES</v>
       </c>
       <c r="B7">
-        <v>6617</v>
+        <v>6619</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>GC MAXUS PKFF-65 G VICENCIO</v>
+        <v>DONGFENG DF6 SRSR-97</v>
       </c>
       <c r="B8">
-        <v>6616</v>
+        <v>6618</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1029,10 +987,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>GC TM5-RXXG-13 D SILVA</v>
+        <v>GC MAXUS PCRF-25 TERRENO</v>
       </c>
       <c r="B9">
-        <v>6608</v>
+        <v>6617</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1043,10 +1001,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>GC TM5-VKFB-85 M CASTRO</v>
+        <v>GC MAXUS PKFF-65 G VICENCIO</v>
       </c>
       <c r="B10">
-        <v>6609</v>
+        <v>6616</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1057,10 +1015,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>GC TM5-VRVJ-20 L SALINAS</v>
+        <v>GC TM5-VKFB-85 M CASTRO</v>
       </c>
       <c r="B11">
-        <v>6620</v>
+        <v>6609</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1071,10 +1029,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>GC TSVS-89 M AEDO</v>
+        <v>GC TM5-VRVJ-20 L SALINAS</v>
       </c>
       <c r="B12">
-        <v>6610</v>
+        <v>6620</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1085,10 +1043,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>GLP ALJIBE SJHW-20</v>
+        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
       </c>
       <c r="B13">
-        <v>6583</v>
+        <v>6593</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1099,10 +1057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
+        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
       </c>
       <c r="B14">
-        <v>6593</v>
+        <v>6597</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1113,10 +1071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
+        <v>GLP SHDV-51 J REBOLLEDO</v>
       </c>
       <c r="B15">
-        <v>6597</v>
+        <v>6598</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1127,10 +1085,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>GLP SHDV-51 J REBOLLEDO</v>
+        <v>GLP SHXP-98 CAMION PLUMA</v>
       </c>
       <c r="B16">
-        <v>6598</v>
+        <v>6604</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1141,10 +1099,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>GLP SHLC-75 L FONSECA</v>
+        <v>GLP SHXP-99 ALZA HOMBRE</v>
       </c>
       <c r="B17">
-        <v>6586</v>
+        <v>6601</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1155,10 +1113,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>GLP SHXP-98 CAMION PLUMA</v>
+        <v>GLP SSZD-71  J VALLEJOS</v>
       </c>
       <c r="B18">
-        <v>6604</v>
+        <v>6580</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1169,10 +1127,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>GLP SHXP-99 ALZA HOMBRE</v>
+        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
       </c>
       <c r="B19">
-        <v>6601</v>
+        <v>6594</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1183,10 +1141,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>GLP SSZD-71  J VALLEJOS</v>
+        <v>GP -SHLC-76 F SEPULVEDA</v>
       </c>
       <c r="B20">
-        <v>6580</v>
+        <v>6605</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1197,10 +1155,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
+        <v>GP CHANGAN RRDF-75 L LOBOS</v>
       </c>
       <c r="B21">
-        <v>6594</v>
+        <v>6603</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1211,10 +1169,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>GP -SHLC-76 F SEPULVEDA</v>
+        <v>GP FOTON G7 TSVS-96</v>
       </c>
       <c r="B22">
-        <v>6605</v>
+        <v>6602</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1225,10 +1183,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>GP CHANGAN RRDF-75 L LOBOS</v>
+        <v>GP TM5 TRRD-32 V PIZARRO</v>
       </c>
       <c r="B23">
-        <v>6603</v>
+        <v>6612</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1239,10 +1197,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>GP DONGFENG DF6-RXDL-60</v>
+        <v>GP TM5 TSDK-95 L MUNOZ</v>
       </c>
       <c r="B24">
-        <v>6607</v>
+        <v>6599</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1253,10 +1211,10 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>GP FOTON G7 TSVS-96</v>
+        <v>GV FOSERO SJHW-18 V OLIVARES</v>
       </c>
       <c r="B25">
-        <v>6602</v>
+        <v>6592</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1267,10 +1225,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>GP TM5 TRRD-32 V PIZARRO</v>
+        <v>GV PEUGEOT THJY-73 J PONCE</v>
       </c>
       <c r="B26">
-        <v>6612</v>
+        <v>6595</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1281,10 +1239,10 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>GP TM5 TSDK-95 L MUNOZ</v>
+        <v>GV SHDV-50 C CARDENAS</v>
       </c>
       <c r="B27">
-        <v>6599</v>
+        <v>6585</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1295,10 +1253,10 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>GV FORD BU-9781 V OLIVARES</v>
+        <v>GV SHLC-74 B MIRANDA</v>
       </c>
       <c r="B28">
-        <v>6621</v>
+        <v>6588</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1309,10 +1267,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>GV FOSERO SJHW-18 V OLIVARES</v>
+        <v>GV TDKV-88 L CORDERO</v>
       </c>
       <c r="B29">
-        <v>6592</v>
+        <v>6587</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1323,10 +1281,10 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>GV PEUGEOT THJY-73 J PONCE</v>
+        <v>GV TDLD-98 J PACHECHO</v>
       </c>
       <c r="B30">
-        <v>6595</v>
+        <v>6582</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1337,10 +1295,10 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>GV SHDV-50 C CARDENAS</v>
+        <v>GV TM5 RXXG-15 E CABANILLA</v>
       </c>
       <c r="B31">
-        <v>6585</v>
+        <v>6589</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1351,10 +1309,10 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>GV SHLC-74 B MIRANDA</v>
+        <v>GV TM5 TDLD-46 M MARTINEZ</v>
       </c>
       <c r="B32">
-        <v>6588</v>
+        <v>6596</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1365,63 +1323,21 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>GV TDKV-88 L CORDERO</v>
+        <v>JAC  LYTS-17 G GALEA</v>
       </c>
       <c r="B33">
-        <v>6587</v>
+        <v>6614</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>GV TDLD-98 J PACHECHO</v>
-      </c>
-      <c r="B34">
-        <v>6582</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>GV TM5 TDLD-46 M MARTINEZ</v>
-      </c>
-      <c r="B35">
-        <v>6596</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>JAC  LYTS-17 G GALEA</v>
-      </c>
-      <c r="B36">
-        <v>6614</v>
-      </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D33"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/latest-events.xlsx
+++ b/latest-events.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -422,7 +422,7 @@
         <v>6618</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-10-13 08:47:03</v>
+        <v>2026-10-19 08:46:50</v>
       </c>
       <c r="D2" t="str">
         <v>NO</v>
@@ -436,7 +436,7 @@
         <v>6617</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-10-14 17:43:07</v>
+        <v>2026-10-20 13:27:19</v>
       </c>
       <c r="D3" t="str">
         <v>NO</v>
@@ -450,7 +450,7 @@
         <v>6616</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-10-12 09:44:37</v>
+        <v>2026-10-19 10:28:08</v>
       </c>
       <c r="D4" t="str">
         <v>NO</v>
@@ -464,10 +464,10 @@
         <v>6608</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-10-12 21:34:09</v>
+        <v>2026-10-19 08:35:10</v>
       </c>
       <c r="D5" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="6">
@@ -478,7 +478,7 @@
         <v>6609</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-10-13 10:19:11</v>
+        <v>2026-10-19 10:21:20</v>
       </c>
       <c r="D6" t="str">
         <v>NO</v>
@@ -492,7 +492,7 @@
         <v>6620</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-10-13 11:14:46</v>
+        <v>2026-10-19 11:34:04</v>
       </c>
       <c r="D7" t="str">
         <v>NO</v>
@@ -506,10 +506,10 @@
         <v>6583</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-10-14 03:11:25</v>
+        <v>2026-10-19 12:08:07</v>
       </c>
       <c r="D8" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="9">
@@ -520,7 +520,7 @@
         <v>6593</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-10-12 15:41:34</v>
+        <v>2026-10-19 12:48:15</v>
       </c>
       <c r="D9" t="str">
         <v>NO</v>
@@ -534,10 +534,10 @@
         <v>6597</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-10-12 10:24:35</v>
+        <v>2026-10-19 06:05:40</v>
       </c>
       <c r="D10" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="11">
@@ -548,7 +548,7 @@
         <v>6598</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-10-12 15:25:43</v>
+        <v>2026-10-19 10:01:46</v>
       </c>
       <c r="D11" t="str">
         <v>NO</v>
@@ -562,10 +562,10 @@
         <v>6586</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-10-13 20:51:31</v>
+        <v>2026-10-19 15:30:08</v>
       </c>
       <c r="D12" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="13">
@@ -576,7 +576,7 @@
         <v>6604</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-10-14 14:36:05</v>
+        <v>2026-10-19 12:50:29</v>
       </c>
       <c r="D13" t="str">
         <v>NO</v>
@@ -590,7 +590,7 @@
         <v>6601</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-10-14 13:51:40</v>
+        <v>2026-10-19 12:22:24</v>
       </c>
       <c r="D14" t="str">
         <v>NO</v>
@@ -604,10 +604,10 @@
         <v>6606</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-10-12 04:00:20</v>
+        <v>2026-10-19 09:37:59</v>
       </c>
       <c r="D15" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="16">
@@ -618,7 +618,7 @@
         <v>6580</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-10-13 12:17:08</v>
+        <v>2026-10-19 10:59:28</v>
       </c>
       <c r="D16" t="str">
         <v>NO</v>
@@ -632,7 +632,7 @@
         <v>6594</v>
       </c>
       <c r="C17" t="str">
-        <v>2026-10-13 11:04:07</v>
+        <v>2026-10-19 11:08:29</v>
       </c>
       <c r="D17" t="str">
         <v>NO</v>
@@ -646,7 +646,7 @@
         <v>6605</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-10-13 11:07:11</v>
+        <v>2026-10-19 10:58:31</v>
       </c>
       <c r="D18" t="str">
         <v>NO</v>
@@ -660,7 +660,7 @@
         <v>6603</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-10-13 09:56:59</v>
+        <v>2026-10-19 11:38:11</v>
       </c>
       <c r="D19" t="str">
         <v>NO</v>
@@ -674,7 +674,7 @@
         <v>6607</v>
       </c>
       <c r="C20" t="str">
-        <v>2026-10-12 05:33:27</v>
+        <v>2026-10-19 04:56:11</v>
       </c>
       <c r="D20" t="str">
         <v>SI</v>
@@ -688,7 +688,7 @@
         <v>6602</v>
       </c>
       <c r="C21" t="str">
-        <v>2026-10-13 14:11:34</v>
+        <v>2026-10-19 09:23:45</v>
       </c>
       <c r="D21" t="str">
         <v>NO</v>
@@ -702,7 +702,7 @@
         <v>6612</v>
       </c>
       <c r="C22" t="str">
-        <v>2026-10-13 11:09:46</v>
+        <v>2026-10-19 10:52:27</v>
       </c>
       <c r="D22" t="str">
         <v>NO</v>
@@ -716,7 +716,7 @@
         <v>6599</v>
       </c>
       <c r="C23" t="str">
-        <v>2026-10-13 10:49:25</v>
+        <v>2026-10-19 10:48:03</v>
       </c>
       <c r="D23" t="str">
         <v>NO</v>
@@ -724,13 +724,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>GV FOSERO SJHW-18 V OLIVARES</v>
+        <v>GV FORD BU-9781 V OLIVARES</v>
       </c>
       <c r="B24">
-        <v>6592</v>
+        <v>6621</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-10-13 07:12:16</v>
+        <v>2026-10-19 18:02:11</v>
       </c>
       <c r="D24" t="str">
         <v>NO</v>
@@ -738,13 +738,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>GV PEUGEOT THJY-73 J PONCE</v>
+        <v>GV FOSERO SJHW-18 V OLIVARES</v>
       </c>
       <c r="B25">
-        <v>6595</v>
+        <v>6592</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-10-13 10:02:35</v>
+        <v>2026-10-19 07:08:35</v>
       </c>
       <c r="D25" t="str">
         <v>NO</v>
@@ -752,13 +752,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>GV SHDV-50 C CARDENAS</v>
+        <v>GV PEUGEOT THJY-73 J PONCE</v>
       </c>
       <c r="B26">
-        <v>6585</v>
+        <v>6595</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-10-13 10:17:31</v>
+        <v>2026-10-19 09:55:28</v>
       </c>
       <c r="D26" t="str">
         <v>NO</v>
@@ -766,13 +766,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>GV SHLC-74 B MIRANDA</v>
+        <v>GV SHDV-50 C CARDENAS</v>
       </c>
       <c r="B27">
-        <v>6588</v>
+        <v>6585</v>
       </c>
       <c r="C27" t="str">
-        <v>2026-10-13 11:01:56</v>
+        <v>2026-10-19 10:17:23</v>
       </c>
       <c r="D27" t="str">
         <v>NO</v>
@@ -780,13 +780,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>GV TDKV-88 L CORDERO</v>
+        <v>GV SHLC-74 B MIRANDA</v>
       </c>
       <c r="B28">
-        <v>6587</v>
+        <v>6588</v>
       </c>
       <c r="C28" t="str">
-        <v>2026-10-13 10:24:10</v>
+        <v>2026-10-19 11:02:21</v>
       </c>
       <c r="D28" t="str">
         <v>NO</v>
@@ -794,13 +794,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>GV TDLD-98 J PACHECHO</v>
+        <v>GV TDKV-88 L CORDERO</v>
       </c>
       <c r="B29">
-        <v>6582</v>
+        <v>6587</v>
       </c>
       <c r="C29" t="str">
-        <v>2026-10-13 14:12:20</v>
+        <v>2026-10-19 10:25:15</v>
       </c>
       <c r="D29" t="str">
         <v>NO</v>
@@ -808,13 +808,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>GV TM5 RXXG-15 E CABANILLA</v>
+        <v>GV TDLD-98 J PACHECHO</v>
       </c>
       <c r="B30">
-        <v>6589</v>
+        <v>6582</v>
       </c>
       <c r="C30" t="str">
-        <v>2026-10-13 12:04:37</v>
+        <v>2026-10-19 10:58:12</v>
       </c>
       <c r="D30" t="str">
         <v>NO</v>
@@ -822,13 +822,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>GV TM5 TDLD-46 M MARTINEZ</v>
+        <v>GV TM5 RXXG-15 E CABANILLA</v>
       </c>
       <c r="B31">
-        <v>6596</v>
+        <v>6589</v>
       </c>
       <c r="C31" t="str">
-        <v>2026-10-13 11:16:29</v>
+        <v>2026-10-19 13:21:06</v>
       </c>
       <c r="D31" t="str">
         <v>NO</v>
@@ -836,42 +836,56 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>GV TOLVA SPGW-29 V OLIVARES</v>
+        <v>GV TM5 TDLD-46 M MARTINEZ</v>
       </c>
       <c r="B32">
-        <v>6619</v>
+        <v>6596</v>
       </c>
       <c r="C32" t="str">
-        <v>2026-10-13 20:35:48</v>
+        <v>2026-10-19 14:16:34</v>
       </c>
       <c r="D32" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
+        <v>GV TOLVA SPGW-29 V OLIVARES</v>
+      </c>
+      <c r="B33">
+        <v>6619</v>
+      </c>
+      <c r="C33" t="str">
+        <v>2026-10-19 13:40:11</v>
+      </c>
+      <c r="D33" t="str">
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
         <v>JAC  LYTS-17 G GALEA</v>
       </c>
-      <c r="B33">
+      <c r="B34">
         <v>6614</v>
       </c>
-      <c r="C33" t="str">
-        <v>2026-10-13 08:47:41</v>
-      </c>
-      <c r="D33" t="str">
+      <c r="C34" t="str">
+        <v>2026-10-19 08:49:14</v>
+      </c>
+      <c r="D34" t="str">
         <v>NO</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D34"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -889,10 +903,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>GC TM5-RXXG-13 D SILVA</v>
+        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
       </c>
       <c r="B2">
-        <v>6608</v>
+        <v>6597</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -903,10 +917,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>GLP ALJIBE SJHW-20</v>
+        <v>GP DONGFENG DF6-RXDL-60</v>
       </c>
       <c r="B3">
-        <v>6583</v>
+        <v>6607</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -917,66 +931,66 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>GLP SHLC-75 L FONSECA</v>
+        <v>DONGFENG DF6 SRSR-97</v>
       </c>
       <c r="B4">
-        <v>6586</v>
+        <v>6618</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>GLP SKDX-44 V VIAL</v>
+        <v>GC MAXUS PCRF-25 TERRENO</v>
       </c>
       <c r="B5">
-        <v>6606</v>
+        <v>6617</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>GP DONGFENG DF6-RXDL-60</v>
+        <v>GC MAXUS PKFF-65 G VICENCIO</v>
       </c>
       <c r="B6">
-        <v>6607</v>
+        <v>6616</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>GV TOLVA SPGW-29 V OLIVARES</v>
+        <v>GC TM5-RXXG-13 D SILVA</v>
       </c>
       <c r="B7">
-        <v>6619</v>
+        <v>6608</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>DONGFENG DF6 SRSR-97</v>
+        <v>GC TM5-VKFB-85 M CASTRO</v>
       </c>
       <c r="B8">
-        <v>6618</v>
+        <v>6609</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -987,10 +1001,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>GC MAXUS PCRF-25 TERRENO</v>
+        <v>GC TM5-VRVJ-20 L SALINAS</v>
       </c>
       <c r="B9">
-        <v>6617</v>
+        <v>6620</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1001,10 +1015,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>GC MAXUS PKFF-65 G VICENCIO</v>
+        <v>GLP ALJIBE SJHW-20</v>
       </c>
       <c r="B10">
-        <v>6616</v>
+        <v>6583</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1015,10 +1029,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>GC TM5-VKFB-85 M CASTRO</v>
+        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
       </c>
       <c r="B11">
-        <v>6609</v>
+        <v>6593</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1029,10 +1043,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>GC TM5-VRVJ-20 L SALINAS</v>
+        <v>GLP SHDV-51 J REBOLLEDO</v>
       </c>
       <c r="B12">
-        <v>6620</v>
+        <v>6598</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1043,10 +1057,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
+        <v>GLP SHLC-75 L FONSECA</v>
       </c>
       <c r="B13">
-        <v>6593</v>
+        <v>6586</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1057,10 +1071,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
+        <v>GLP SHXP-98 CAMION PLUMA</v>
       </c>
       <c r="B14">
-        <v>6597</v>
+        <v>6604</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1071,10 +1085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>GLP SHDV-51 J REBOLLEDO</v>
+        <v>GLP SHXP-99 ALZA HOMBRE</v>
       </c>
       <c r="B15">
-        <v>6598</v>
+        <v>6601</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1085,10 +1099,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>GLP SHXP-98 CAMION PLUMA</v>
+        <v>GLP SKDX-44 V VIAL</v>
       </c>
       <c r="B16">
-        <v>6604</v>
+        <v>6606</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1099,10 +1113,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>GLP SHXP-99 ALZA HOMBRE</v>
+        <v>GLP SSZD-71  J VALLEJOS</v>
       </c>
       <c r="B17">
-        <v>6601</v>
+        <v>6580</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1113,10 +1127,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>GLP SSZD-71  J VALLEJOS</v>
+        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
       </c>
       <c r="B18">
-        <v>6580</v>
+        <v>6594</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1127,10 +1141,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
+        <v>GP -SHLC-76 F SEPULVEDA</v>
       </c>
       <c r="B19">
-        <v>6594</v>
+        <v>6605</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1141,10 +1155,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>GP -SHLC-76 F SEPULVEDA</v>
+        <v>GP CHANGAN RRDF-75 L LOBOS</v>
       </c>
       <c r="B20">
-        <v>6605</v>
+        <v>6603</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1155,10 +1169,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>GP CHANGAN RRDF-75 L LOBOS</v>
+        <v>GP FOTON G7 TSVS-96</v>
       </c>
       <c r="B21">
-        <v>6603</v>
+        <v>6602</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1169,10 +1183,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>GP FOTON G7 TSVS-96</v>
+        <v>GP TM5 TRRD-32 V PIZARRO</v>
       </c>
       <c r="B22">
-        <v>6602</v>
+        <v>6612</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1183,10 +1197,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>GP TM5 TRRD-32 V PIZARRO</v>
+        <v>GP TM5 TSDK-95 L MUNOZ</v>
       </c>
       <c r="B23">
-        <v>6612</v>
+        <v>6599</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1197,10 +1211,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>GP TM5 TSDK-95 L MUNOZ</v>
+        <v>GV FORD BU-9781 V OLIVARES</v>
       </c>
       <c r="B24">
-        <v>6599</v>
+        <v>6621</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1323,21 +1337,35 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
+        <v>GV TOLVA SPGW-29 V OLIVARES</v>
+      </c>
+      <c r="B33">
+        <v>6619</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
         <v>JAC  LYTS-17 G GALEA</v>
       </c>
-      <c r="B33">
+      <c r="B34">
         <v>6614</v>
       </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D34"/>
   </ignoredErrors>
 </worksheet>
 </file>